--- a/00-TrainRnns/tau-6/Y_otm/BestModels-otm.xlsx
+++ b/00-TrainRnns/tau-6/Y_otm/BestModels-otm.xlsx
@@ -477,182 +477,182 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>37</v>
+        <v>481</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>model_arch2_r0.9_Ld0.5_Lp0.5_seed8467</t>
+          <t>model_arch17_r0.01_Ld0.5_Lp0.5_seed6686</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[2]</t>
+          <t>[17]</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9988652863796194</v>
+        <v>0.9994188277498586</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9405077525771146</v>
+        <v>0.9911830942707265</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5447679954491826</v>
+        <v>0.9227275924943591</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9988652863796194</v>
+        <v>0.9994188277498586</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9405077525771146</v>
+        <v>0.9911830942707265</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5447679954491826</v>
+        <v>0.9227275924943591</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7950609445941915</v>
+        <v>0.9571885282761617</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>31</v>
+        <v>609</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>model_arch2_r0.01_Ld0.5_Lp0.5_seed6686</t>
+          <t>model_arch21_r0.9_Ld0.5_Lp0.5_seed5011</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[2]</t>
+          <t>[21]</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.999682297921317</v>
+        <v>0.9957674201010379</v>
       </c>
       <c r="E3" t="n">
-        <v>0.915816972334615</v>
+        <v>0.9871817620484028</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5481580602936109</v>
+        <v>0.8466944289482148</v>
       </c>
       <c r="G3" t="n">
-        <v>0.999682297921317</v>
+        <v>0.9957674201010379</v>
       </c>
       <c r="H3" t="n">
-        <v>0.915816972334615</v>
+        <v>0.9871817620484028</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5481580602936109</v>
+        <v>0.8466944289482148</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7889902371843767</v>
+        <v>0.9254124891362059</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>40</v>
+        <v>1285</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>model_arch2_r0.01_Ld0.3_Lp0.7_seed9974</t>
+          <t>model_arch43_r0.9_Ld0.7_Lp0.3_seed9974</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[2]</t>
+          <t>[43]</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9993427786761027</v>
+        <v>0.998170346066948</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9109929292990013</v>
+        <v>0.9603017077503203</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5380375240361279</v>
+        <v>0.8546708083780734</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9993427786761027</v>
+        <v>0.998170346066948</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9109929292990013</v>
+        <v>0.9603017077503203</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5380375240361279</v>
+        <v>0.8546708083780734</v>
       </c>
       <c r="J4" t="n">
-        <v>0.78347834241492</v>
+        <v>0.9209002950585637</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>36</v>
+        <v>1280</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>model_arch2_r0.9_Ld0.5_Lp0.5_seed6686</t>
+          <t>model_arch43_r0.01_Ld0.7_Lp0.3_seed9974</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[2]</t>
+          <t>[43]</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9964151931425466</v>
+        <v>0.999044183047887</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9279946352091989</v>
+        <v>0.9431759008252529</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4810241146147718</v>
+        <v>0.8570363452938368</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9964151931425466</v>
+        <v>0.999044183047887</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9279946352091989</v>
+        <v>0.9431759008252529</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4810241146147718</v>
+        <v>0.8570363452938368</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7658023698570581</v>
+        <v>0.9166006583914303</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>4</v>
+        <v>115</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>model_arch1_r0.01_Ld0.5_Lp0.5_seed5011</t>
+          <t>model_arch4_r0.9_Ld0.7_Lp0.3_seed9974</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>[4]</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9898044573706059</v>
+        <v>0.9988865761514648</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5579885313981974</v>
+        <v>0.9641233901295312</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7852450586618437</v>
+        <v>0.825889882449269</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9898044573706059</v>
+        <v>0.9988865761514648</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5579885313981974</v>
+        <v>0.9641233901295312</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7852450586618437</v>
+        <v>0.825889882449269</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7483018199120424</v>
+        <v>0.9111859175545567</v>
       </c>
     </row>
   </sheetData>

--- a/00-TrainRnns/tau-6/Y_otm/BestModels-otm.xlsx
+++ b/00-TrainRnns/tau-6/Y_otm/BestModels-otm.xlsx
@@ -549,110 +549,110 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1285</v>
+        <v>2401</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>model_arch43_r0.9_Ld0.7_Lp0.3_seed9974</t>
+          <t>model_arch79_r0.9_Ld0.5_Lp0.5_seed922</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[43]</t>
+          <t>[79]</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.998170346066948</v>
+        <v>0.9980660991818672</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9603017077503203</v>
+        <v>0.9876471213516187</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8546708083780734</v>
+        <v>0.8402451746862865</v>
       </c>
       <c r="G4" t="n">
-        <v>0.998170346066948</v>
+        <v>0.9980660991818672</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9603017077503203</v>
+        <v>0.9876471213516187</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8546708083780734</v>
+        <v>0.8402451746862865</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9209002950585637</v>
+        <v>0.9237398580531648</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>1280</v>
+        <v>2857</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>model_arch43_r0.01_Ld0.7_Lp0.3_seed9974</t>
+          <t>model_arch94_r0.9_Ld0.3_Lp0.7_seed1932</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[43]</t>
+          <t>[94]</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.999044183047887</v>
+        <v>0.9970878039251424</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9431759008252529</v>
+        <v>0.938741393416159</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8570363452938368</v>
+        <v>0.880717210462012</v>
       </c>
       <c r="G5" t="n">
-        <v>0.999044183047887</v>
+        <v>0.9970878039251424</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9431759008252529</v>
+        <v>0.938741393416159</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8570363452938368</v>
+        <v>0.880717210462012</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9166006583914303</v>
+        <v>0.9236417774666013</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>115</v>
+        <v>1285</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>model_arch4_r0.9_Ld0.7_Lp0.3_seed9974</t>
+          <t>model_arch43_r0.9_Ld0.7_Lp0.3_seed9974</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[4]</t>
+          <t>[43]</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9988865761514648</v>
+        <v>0.998170346066948</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9641233901295312</v>
+        <v>0.9603017077503203</v>
       </c>
       <c r="F6" t="n">
-        <v>0.825889882449269</v>
+        <v>0.8546708083780734</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9988865761514648</v>
+        <v>0.998170346066948</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9641233901295312</v>
+        <v>0.9603017077503203</v>
       </c>
       <c r="I6" t="n">
-        <v>0.825889882449269</v>
+        <v>0.8546708083780734</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9111859175545567</v>
+        <v>0.9209002950585637</v>
       </c>
     </row>
   </sheetData>
